--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G28"/>
+  <dimension ref="A2:G38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -703,16 +703,16 @@
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>10001</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>붕어</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -721,172 +721,148 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Military1</t>
-        </is>
-      </c>
+        <v>9999</v>
+      </c>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="5" t="n">
-        <v>2</v>
+        <v>10002</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>잉어</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Military2</t>
-        </is>
-      </c>
+        <v>9999</v>
+      </c>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>10003</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>월척 붕어</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Military3</t>
-        </is>
-      </c>
+        <v>9999</v>
+      </c>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="5" t="n">
-        <v>4</v>
+        <v>10004</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>향어</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Shaman1</t>
-        </is>
-      </c>
+        <v>9999</v>
+      </c>
+      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="5" t="n">
-        <v>5</v>
+        <v>10005</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>대물 잉어</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Shaman2</t>
-        </is>
-      </c>
+        <v>9999</v>
+      </c>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="5" t="n">
-        <v>6</v>
+        <v>10006</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>전설의 잉어</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Misc</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>304</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Shaman3</t>
-        </is>
-      </c>
+        <v>9999</v>
+      </c>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="5" t="n">
-        <v>1001</v>
+        <v>20001</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>일반 생선</t>
+          <t>밀</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -902,16 +878,16 @@
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="5" t="n">
-        <v>1002</v>
+        <v>20002</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>고급 생선</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -927,16 +903,16 @@
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="5" t="n">
-        <v>1003</v>
+        <v>20003</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>희귀 생선</t>
+          <t>옥수수</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -952,16 +928,16 @@
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="5" t="n">
-        <v>1004</v>
+        <v>20004</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>영웅 생선</t>
+          <t>인삼</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -977,16 +953,16 @@
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="5" t="n">
-        <v>1005</v>
+        <v>20005</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>전설 생선</t>
+          <t>변종 인삼</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1002,16 +978,16 @@
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="5" t="n">
-        <v>1006</v>
+        <v>20006</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>희귀 생선</t>
+          <t>태초의 씨앗</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1026,75 +1002,433 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="B21" s="5" t="n">
+        <v>30001</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>잡목</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="B22" s="5" t="n">
+        <v>30002</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>소나무 목재</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="B23" s="5" t="n">
+        <v>30003</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>참나무 목재</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="B24" s="5" t="n">
+        <v>30004</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>흑단 목재</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="B25" s="5" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>고급 원목</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="B26" s="5" t="n">
+        <v>30006</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>세계수 가지</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
+      <c r="B27" s="5" t="n">
+        <v>40001</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>돌덩어리</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
+      <c r="B28" s="5" t="n">
+        <v>40002</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>구리 광석</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>9999</v>
+      </c>
       <c r="G28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>40003</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>은광석</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>40004</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>금광석</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>40005</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>보석 원석</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>40006</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>심연의 원석</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>50001</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>질긴 고기</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>50002</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>토끼 가죽</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>50003</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>늑대 가죽</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>50004</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>곰 모피</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>50005</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>거대한 뿔</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>50006</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>마수의 심장</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>9999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G38"/>
+  <dimension ref="A2:G158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,11 @@
       <c r="F9" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>개울(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -748,7 +752,11 @@
       <c r="F10" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>개울(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -773,7 +781,11 @@
       <c r="F11" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>개울(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
@@ -798,7 +810,11 @@
       <c r="F12" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>개울(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -823,7 +839,11 @@
       <c r="F13" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>개울(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
@@ -848,7 +868,11 @@
       <c r="F14" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>개울(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="4" t="n"/>
@@ -873,7 +897,11 @@
       <c r="F15" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G15" s="7" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>텃밭(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -898,7 +926,11 @@
       <c r="F16" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>텃밭(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -923,7 +955,11 @@
       <c r="F17" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>텃밭(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -948,7 +984,11 @@
       <c r="F18" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G18" s="7" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>텃밭(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -973,7 +1013,11 @@
       <c r="F19" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G19" s="7" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>텃밭(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -998,7 +1042,11 @@
       <c r="F20" s="5" t="n">
         <v>9999</v>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>텃밭(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1023,7 +1071,11 @@
       <c r="F21" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>잡목림(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1048,7 +1100,11 @@
       <c r="F22" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G22" s="7" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>잡목림(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1073,7 +1129,11 @@
       <c r="F23" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G23" s="7" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>잡목림(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1098,7 +1158,11 @@
       <c r="F24" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G24" s="7" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>잡목림(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1123,7 +1187,11 @@
       <c r="F25" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G25" s="7" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>잡목림(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1148,7 +1216,11 @@
       <c r="F26" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>잡목림(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1173,7 +1245,11 @@
       <c r="F27" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G27" s="7" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>노천 광산(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1198,7 +1274,11 @@
       <c r="F28" s="7" t="n">
         <v>9999</v>
       </c>
-      <c r="G28" s="7" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>노천 광산(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
@@ -1222,6 +1302,11 @@
       <c r="F29" t="n">
         <v>9999</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>노천 광산(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
@@ -1245,6 +1330,11 @@
       <c r="F30" t="n">
         <v>9999</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>노천 광산(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -1268,6 +1358,11 @@
       <c r="F31" t="n">
         <v>9999</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>노천 광산(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -1291,6 +1386,11 @@
       <c r="F32" t="n">
         <v>9999</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>노천 광산(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -1314,6 +1414,11 @@
       <c r="F33" t="n">
         <v>9999</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>들판(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -1337,6 +1442,11 @@
       <c r="F34" t="n">
         <v>9999</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>들판(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -1360,6 +1470,11 @@
       <c r="F35" t="n">
         <v>9999</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>들판(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -1383,6 +1498,11 @@
       <c r="F36" t="n">
         <v>9999</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>들판(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
@@ -1406,6 +1526,11 @@
       <c r="F37" t="n">
         <v>9999</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>들판(Lv1)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
@@ -1428,6 +1553,3371 @@
       </c>
       <c r="F38" t="n">
         <v>9999</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>들판(Lv1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>피라미</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>저수지(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>10012</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>메기</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>저수지(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>10013</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>가물치</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>저수지(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>10014</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>백년 메기</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>저수지(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>10015</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>저수지의 주인</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>저수지(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>용왕의 사자</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>저수지(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>10021</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>모래무지</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>강 하류(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>10022</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>쏘가리</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>강 하류(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>10023</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>황금 잉어</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>강 하류(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>10024</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>강의 수호자</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>강 하류(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>10025</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>천년 쏘가리</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>강 하류(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>10026</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>강신의 비늘</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>강 하류(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>10031</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>빙어</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>호수(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>10032</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>송어</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>호수(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>10033</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>무지개 송어</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>호수(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>10034</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>호수의 눈</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>호수(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>10035</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>심층 대어</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>호수(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>10036</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>호수의 심장</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>호수(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>10041</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>심해 새우</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>심해(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>10042</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>아귀</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>심해(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>10043</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>심해 등불고기</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>심해(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>10044</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>대왕오징어</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>심해(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>10045</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>해구의 지배자</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>심해(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>10046</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>리바이어던의 조각</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>심해(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>20011</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>보리</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>밭(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>20012</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>고구마</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>밭(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>20013</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>호박</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>밭(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>백년초</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>밭(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>20015</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>황금 호박</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>밭(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>20016</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>불멸의 뿌리</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>밭(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>20021</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>벼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>농장(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>20022</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>콩</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>농장(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>20023</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>딸기</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>농장(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>20024</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>산삼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>농장(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>20025</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>천년 산삼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>농장(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>20026</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>생명의 열매</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>농장(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>20031</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>목화</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>대농장(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>20032</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>사탕수수</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>대농장(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>20033</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>커피 열매</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>대농장(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>20034</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>흑진주 포도</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>대농장(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>20035</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>무지개 밀</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>대농장(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>20036</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>세계수의 씨앗</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>대농장(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>20041</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>정화된 흙</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>신성한 대지(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>20042</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>성스러운 이삭</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>신성한 대지(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>20043</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>영약초</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>신성한 대지(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>20044</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>신월초</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>신성한 대지(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>20045</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>신들의 곡식</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>신성한 대지(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>20046</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>창세의 열매</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>신성한 대지(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>30011</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>잔가지</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>소나무 숲(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>30012</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>삼나무 목재</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>소나무 숲(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>30013</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>편백나무 목재</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>소나무 숲(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>30014</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>홍송 원목</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>소나무 숲(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>30015</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>천년 소나무</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>소나무 숲(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>30016</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>숲의 정령목</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>소나무 숲(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>30021</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>도토리 가지</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>참나무 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>30022</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>너도밤나무 목재</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>참나무 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>30023</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>단풍나무 목재</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>참나무 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>30024</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>고목의 심재</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>참나무 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>30025</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>백년 참나무</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>참나무 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>30026</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>대지의 뿌리</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>참나무 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>30031</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>그을린 통나무</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>흑림(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>30032</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>흑참나무 목재</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>흑림(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>30033</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>자단 목재</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>흑림(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>30034</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>마력 깃든 목재</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>흑림(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>30035</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>흑림의 고목</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>흑림(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>30036</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>어둠나무의 핵</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>흑림(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>30041</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>세계수 껍질</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>세계수 뿌리(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>30042</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>빛나는 수액</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>세계수 뿌리(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>30043</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>신목 목재</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>세계수 뿌리(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>30044</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>영원의 나이테</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>세계수 뿌리(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>30045</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>세계수 심재</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>세계수 뿌리(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>30046</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>창세목의 조각</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>세계수 뿌리(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>40011</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>석회암</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>갱도(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>40012</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>주석 광석</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>갱도(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>40013</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>철광석</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>갱도(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>40014</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>백금 광석</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>갱도(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>40015</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>청옥 원석</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>갱도(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>40016</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>지맥의 결정</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>갱도(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>40021</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>현무암</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>심층 갱도(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>40022</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>아연 광석</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>심층 갱도(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>40023</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>미스릴 광석</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>심층 갱도(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>40024</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>홍옥 원석</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>심층 갱도(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>40025</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>흑요석 결정</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>심층 갱도(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>40026</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>대지의 핵</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>심층 갱도(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>40031</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>수정 파편</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>지하 대공동(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>40032</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>코발트 광석</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>지하 대공동(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>40033</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>오리하르콘 광석</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>지하 대공동(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>40034</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>자수정 원석</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>지하 대공동(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>40035</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>별빛 광석</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>지하 대공동(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>40036</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>공동의 심장</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>지하 대공동(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>40041</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>심연의 파편</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>심연(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>40042</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>암흑 광석</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>심연(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>40043</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>아다만트 광석</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>심연(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>40044</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>심연의 수정</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>심연(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>40045</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>용해된 별의 조각</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>심연(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>40046</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>세계의 축</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>심연(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>50011</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>여우 가죽</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>야산(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>50012</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>멧돼지 엄니</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>야산(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>50013</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>사슴뿔</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>야산(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>50014</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>산군의 발톱</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>야산(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>50015</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>백호의 털</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>야산(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>50016</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>산신의 인장</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>야산(Lv2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>50021</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>표범 가죽</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>깊은 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>50022</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>큰뿔 사슴뿔</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>깊은 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>50023</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>곰의 이빨</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>깊은 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>50024</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>숲괴수의 발톱</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>깊은 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>50025</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>고대 짐승의 뼈</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>깊은 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>50026</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>숲 지배자의 눈</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>깊은 숲(Lv3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>50031</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>설표 가죽</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>설산(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>50032</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>얼음늑대 송곳니</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>설산(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>50033</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>서리곰 모피</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>설산(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>50034</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>빙룡의 비늘</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>설산(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>50035</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>설산 주인의 뿔</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>설산(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>50036</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>영구동토의 심장</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>설산(Lv4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>50041</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>마수의 가죽</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>마수의 영역(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>50042</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>마물의 뿔</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>마수의 영역(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>50043</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>흉수의 송곳니</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>마수의 영역(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>50044</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>마수왕의 갈기</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>마수의 영역(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>50045</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>심연수의 눈</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>마수의 영역(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>50046</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>마신의 파편</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>마수의 영역(Lv5)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G158"/>
+  <dimension ref="A2:G164"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아이템 레어도 </t>
+          <t>레어도 (전역 등급)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>eItemRarity</t>
+          <t>eGlobalRarity</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ItemRarity</t>
+          <t>GlobalRarity</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4917,6 +4917,174 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>100001</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>유리 구슬</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>가챠 전용(테스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>100002</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>호박 구슬</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>가챠 전용(테스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>100003</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>진주 구슬</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>가챠 전용(테스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>100004</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>오팔 구슬</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>가챠 전용(테스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>100005</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>용안 구슬</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>가챠 전용(테스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>100006</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>창세의 구슬</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>가챠 전용(테스트)</t>
         </is>
       </c>
     </row>
